--- a/Paintshop_Schedule_November.xlsx
+++ b/Paintshop_Schedule_November.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,13 +506,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G2" t="n">
         <v>8.333333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -532,35 +532,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>17.09523809523809</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
+        <v>26.61904761904762</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>4.61904761904762</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>55.42857142857144</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>55.42857142857144</v>
       </c>
     </row>
     <row r="4">
@@ -584,13 +584,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>8.095238095238095</v>
       </c>
       <c r="G5" t="n">
-        <v>7.083333333333333</v>
+        <v>8.095238095238095</v>
       </c>
       <c r="H5" t="n">
         <v>15</v>
@@ -653,31 +653,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>18.57142857142857</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>6.190476190476191</v>
       </c>
       <c r="G6" t="n">
-        <v>49.5</v>
+        <v>24.76190476190476</v>
       </c>
       <c r="H6" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I6" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>121.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>121.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -695,28 +695,28 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>30.55555555555556</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G7" t="n">
-        <v>39.44444444444444</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7" t="n">
-        <v>8.444444444444443</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>92.88888888888887</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92.88888888888887</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -734,28 +734,28 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>24.76190476190476</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="H8" t="n">
         <v>35</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -766,35 +766,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>49.44444444444444</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>61.11111111111111</v>
+        <v>39.44444444444444</v>
       </c>
       <c r="H9" t="n">
         <v>38</v>
       </c>
       <c r="I9" t="n">
-        <v>23.11111111111111</v>
+        <v>1.444444444444443</v>
       </c>
       <c r="J9" t="n">
-        <v>300.4444444444444</v>
+        <v>18.77777777777776</v>
       </c>
       <c r="K9" t="n">
-        <v>300.4444444444444</v>
+        <v>18.77777777777776</v>
       </c>
     </row>
     <row r="10">
@@ -805,35 +805,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>37.66666666666666</v>
+        <v>17.22222222222222</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G10" t="n">
-        <v>45.58333333333333</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="H10" t="n">
         <v>32</v>
       </c>
       <c r="I10" t="n">
-        <v>13.58333333333333</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>95.0833333333333</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>95.0833333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -848,31 +848,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>49.58333333333333</v>
+        <v>27.61904761904762</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="G11" t="n">
-        <v>54.58333333333333</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I11" t="n">
-        <v>11.58333333333333</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>115.8333333333333</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>115.8333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -883,35 +883,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>17.08333333333333</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G12" t="n">
-        <v>26.66666666666666</v>
+        <v>21.11111111111111</v>
       </c>
       <c r="H12" t="n">
         <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>6.666666666666664</v>
+        <v>1.111111111111114</v>
       </c>
       <c r="J12" t="n">
-        <v>59.99999999999998</v>
+        <v>13.33333333333337</v>
       </c>
       <c r="K12" t="n">
-        <v>59.99999999999998</v>
+        <v>13.33333333333337</v>
       </c>
     </row>
     <row r="13">
@@ -922,35 +922,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>14.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G13" t="n">
-        <v>26.55555555555556</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="H13" t="n">
         <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>8.555555555555557</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>51.33333333333334</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>51.33333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -961,35 +961,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>54.58333333333333</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5.238095238095238</v>
       </c>
       <c r="G14" t="n">
-        <v>59.16666666666666</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I14" t="n">
-        <v>10.16666666666666</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>111.8333333333333</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>111.8333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1007,28 +1007,28 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>49.5</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>11.90476190476191</v>
       </c>
       <c r="G15" t="n">
-        <v>62</v>
+        <v>50.57142857142857</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>0.5714285714285694</v>
       </c>
       <c r="J15" t="n">
-        <v>196</v>
+        <v>7.999999999999972</v>
       </c>
       <c r="K15" t="n">
-        <v>196</v>
+        <v>7.999999999999972</v>
       </c>
     </row>
     <row r="16">
@@ -1039,35 +1039,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>62.11111111111111</v>
+        <v>52.33333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>11.42857142857143</v>
       </c>
       <c r="G16" t="n">
-        <v>75.44444444444444</v>
+        <v>63.76190476190477</v>
       </c>
       <c r="H16" t="n">
         <v>66</v>
       </c>
       <c r="I16" t="n">
-        <v>9.444444444444443</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>84.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>84.99999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1078,35 +1078,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>70.91666666666666</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G17" t="n">
-        <v>77.58333333333333</v>
+        <v>61.55555555555556</v>
       </c>
       <c r="H17" t="n">
         <v>63</v>
       </c>
       <c r="I17" t="n">
-        <v>14.58333333333333</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>116.6666666666666</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>116.6666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1117,35 +1117,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>97.44444444444446</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G18" t="n">
-        <v>105</v>
+        <v>105.2222222222222</v>
       </c>
       <c r="H18" t="n">
         <v>85</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>20.22222222222223</v>
       </c>
       <c r="J18" t="n">
-        <v>240</v>
+        <v>262.888888888889</v>
       </c>
       <c r="K18" t="n">
-        <v>240</v>
+        <v>262.888888888889</v>
       </c>
     </row>
     <row r="19">
@@ -1166,25 +1166,25 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>75.44444444444444</v>
+        <v>61.55555555555556</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>87.11111111111111</v>
+        <v>73.22222222222223</v>
       </c>
       <c r="H19" t="n">
         <v>78</v>
       </c>
       <c r="I19" t="n">
-        <v>9.111111111111114</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>91.11111111111114</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>91.11111111111114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>77.58333333333333</v>
+        <v>58.11111111111111</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G20" t="n">
-        <v>85.91666666666666</v>
+        <v>69.22222222222221</v>
       </c>
       <c r="H20" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I20" t="n">
-        <v>11.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>178.7499999999999</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>178.7499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1238,31 +1238,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>79.5</v>
+        <v>50.57142857142857</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>7.142857142857143</v>
       </c>
       <c r="G21" t="n">
-        <v>87</v>
+        <v>57.71428571428572</v>
       </c>
       <c r="H21" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1277,31 +1277,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>63</v>
+        <v>62.71428571428572</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>8.095238095238095</v>
       </c>
       <c r="G22" t="n">
-        <v>71.5</v>
+        <v>70.80952380952381</v>
       </c>
       <c r="H22" t="n">
         <v>69</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>1.80952380952381</v>
       </c>
       <c r="J22" t="n">
-        <v>17.5</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>17.5</v>
+        <v>12.66666666666667</v>
       </c>
     </row>
     <row r="23">
@@ -1312,35 +1312,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>94.91666666666666</v>
+        <v>100.1111111111111</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G23" t="n">
-        <v>100.3333333333333</v>
+        <v>107.3333333333333</v>
       </c>
       <c r="H23" t="n">
         <v>86</v>
       </c>
       <c r="I23" t="n">
-        <v>14.33333333333333</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="J23" t="n">
-        <v>143.3333333333333</v>
+        <v>213.3333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>143.3333333333333</v>
+        <v>213.3333333333334</v>
       </c>
     </row>
     <row r="24">
@@ -1351,35 +1351,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>103.3333333333333</v>
+        <v>97.47619047619047</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="G24" t="n">
-        <v>110.8333333333333</v>
+        <v>106.047619047619</v>
       </c>
       <c r="H24" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I24" t="n">
-        <v>6.833333333333329</v>
+        <v>7.047619047619037</v>
       </c>
       <c r="J24" t="n">
-        <v>61.49999999999996</v>
+        <v>63.42857142857133</v>
       </c>
       <c r="K24" t="n">
-        <v>61.49999999999996</v>
+        <v>63.42857142857133</v>
       </c>
     </row>
     <row r="25">
@@ -1394,31 +1394,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
+        <v>108.047619047619</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9.047619047619047</v>
+      </c>
+      <c r="G25" t="n">
+        <v>117.0952380952381</v>
+      </c>
+      <c r="H25" t="n">
         <v>106</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>113</v>
-      </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>11.09523809523809</v>
       </c>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>144.2380952380951</v>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
+        <v>144.2380952380951</v>
       </c>
     </row>
     <row r="26">
@@ -1429,35 +1429,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>59.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>67.91666666666666</v>
+        <v>49.66666666666666</v>
       </c>
       <c r="H26" t="n">
         <v>53</v>
       </c>
       <c r="I26" t="n">
-        <v>14.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>208.8333333333332</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>208.8333333333332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1468,35 +1468,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>87</v>
+        <v>78.22222222222223</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G27" t="n">
-        <v>98</v>
+        <v>90.44444444444446</v>
       </c>
       <c r="H27" t="n">
         <v>81</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>9.444444444444457</v>
       </c>
       <c r="J27" t="n">
-        <v>187</v>
+        <v>85.00000000000011</v>
       </c>
       <c r="K27" t="n">
-        <v>187</v>
+        <v>85.00000000000011</v>
       </c>
     </row>
     <row r="28">
@@ -1511,31 +1511,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>85.91666666666666</v>
+        <v>65.76190476190476</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="G28" t="n">
-        <v>90.91666666666666</v>
+        <v>71.47619047619047</v>
       </c>
       <c r="H28" t="n">
         <v>78</v>
       </c>
       <c r="I28" t="n">
-        <v>12.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>103.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>103.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1546,35 +1546,698 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>92.11111111111111</v>
+        <v>86.52380952380952</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>10.95238095238095</v>
       </c>
       <c r="G29" t="n">
-        <v>104.8888888888889</v>
+        <v>97.47619047619047</v>
       </c>
       <c r="H29" t="n">
         <v>82</v>
       </c>
       <c r="I29" t="n">
-        <v>22.88888888888889</v>
+        <v>15.47619047619047</v>
       </c>
       <c r="J29" t="n">
-        <v>137.3333333333333</v>
+        <v>92.8571428571428</v>
       </c>
       <c r="K29" t="n">
-        <v>137.3333333333333</v>
+        <v>92.8571428571428</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ORD29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>119.4285714285714</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="G30" t="n">
+        <v>124.6666666666667</v>
+      </c>
+      <c r="H30" t="n">
+        <v>110</v>
+      </c>
+      <c r="I30" t="n">
+        <v>14.66666666666666</v>
+      </c>
+      <c r="J30" t="n">
+        <v>131.9999999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>131.9999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ORD30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>124.6666666666667</v>
+      </c>
+      <c r="F31" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="G31" t="n">
+        <v>136.0952380952381</v>
+      </c>
+      <c r="H31" t="n">
+        <v>115</v>
+      </c>
+      <c r="I31" t="n">
+        <v>21.09523809523807</v>
+      </c>
+      <c r="J31" t="n">
+        <v>274.238095238095</v>
+      </c>
+      <c r="K31" t="n">
+        <v>274.238095238095</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ORD31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>103.8571428571428</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="G32" t="n">
+        <v>112.4285714285714</v>
+      </c>
+      <c r="H32" t="n">
+        <v>99</v>
+      </c>
+      <c r="I32" t="n">
+        <v>13.42857142857142</v>
+      </c>
+      <c r="J32" t="n">
+        <v>120.8571428571427</v>
+      </c>
+      <c r="K32" t="n">
+        <v>120.8571428571427</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ORD32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>112.3333333333333</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="G33" t="n">
+        <v>122.8888888888889</v>
+      </c>
+      <c r="H33" t="n">
+        <v>106</v>
+      </c>
+      <c r="I33" t="n">
+        <v>16.8888888888889</v>
+      </c>
+      <c r="J33" t="n">
+        <v>202.6666666666668</v>
+      </c>
+      <c r="K33" t="n">
+        <v>202.6666666666668</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ORD33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>42.33333333333334</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" t="n">
+        <v>52.33333333333334</v>
+      </c>
+      <c r="H34" t="n">
+        <v>53</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ORD34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>71.47619047619047</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10.47619047619048</v>
+      </c>
+      <c r="G35" t="n">
+        <v>81.95238095238095</v>
+      </c>
+      <c r="H35" t="n">
+        <v>80</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.952380952380949</v>
+      </c>
+      <c r="J35" t="n">
+        <v>21.47619047619044</v>
+      </c>
+      <c r="K35" t="n">
+        <v>21.47619047619044</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ORD35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>70.22222222222221</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="G36" t="n">
+        <v>76.88888888888889</v>
+      </c>
+      <c r="H36" t="n">
+        <v>78</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ORD36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>81.95238095238095</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10.95238095238095</v>
+      </c>
+      <c r="G37" t="n">
+        <v>92.9047619047619</v>
+      </c>
+      <c r="H37" t="n">
+        <v>82</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10.9047619047619</v>
+      </c>
+      <c r="J37" t="n">
+        <v>65.42857142857139</v>
+      </c>
+      <c r="K37" t="n">
+        <v>65.42857142857139</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ORD37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>117.0952380952381</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="G38" t="n">
+        <v>122.3333333333333</v>
+      </c>
+      <c r="H38" t="n">
+        <v>110</v>
+      </c>
+      <c r="I38" t="n">
+        <v>12.33333333333333</v>
+      </c>
+      <c r="J38" t="n">
+        <v>111</v>
+      </c>
+      <c r="K38" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ORD38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>126.7777777777778</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="G39" t="n">
+        <v>140.1111111111111</v>
+      </c>
+      <c r="H39" t="n">
+        <v>115</v>
+      </c>
+      <c r="I39" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="J39" t="n">
+        <v>326.4444444444445</v>
+      </c>
+      <c r="K39" t="n">
+        <v>326.4444444444445</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ORD39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>105.2222222222222</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" t="n">
+        <v>115.2222222222222</v>
+      </c>
+      <c r="H40" t="n">
+        <v>99</v>
+      </c>
+      <c r="I40" t="n">
+        <v>16.22222222222223</v>
+      </c>
+      <c r="J40" t="n">
+        <v>146.0000000000001</v>
+      </c>
+      <c r="K40" t="n">
+        <v>146.0000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ORD40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>116.2222222222222</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="G41" t="n">
+        <v>126.7777777777778</v>
+      </c>
+      <c r="H41" t="n">
+        <v>106</v>
+      </c>
+      <c r="I41" t="n">
+        <v>20.77777777777779</v>
+      </c>
+      <c r="J41" t="n">
+        <v>249.3333333333334</v>
+      </c>
+      <c r="K41" t="n">
+        <v>249.3333333333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ORD41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>46.44444444444444</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="G42" t="n">
+        <v>58.11111111111111</v>
+      </c>
+      <c r="H42" t="n">
+        <v>53</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.111111111111107</v>
+      </c>
+      <c r="J42" t="n">
+        <v>71.5555555555555</v>
+      </c>
+      <c r="K42" t="n">
+        <v>71.5555555555555</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ORD42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="n">
+        <v>86.88888888888889</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12.22222222222222</v>
+      </c>
+      <c r="G43" t="n">
+        <v>99.11111111111111</v>
+      </c>
+      <c r="H43" t="n">
+        <v>81</v>
+      </c>
+      <c r="I43" t="n">
+        <v>18.11111111111111</v>
+      </c>
+      <c r="J43" t="n">
+        <v>199.2222222222223</v>
+      </c>
+      <c r="K43" t="n">
+        <v>199.2222222222223</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ORD43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>71.80952380952381</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="G44" t="n">
+        <v>77.52380952380952</v>
+      </c>
+      <c r="H44" t="n">
+        <v>78</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ORD44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>9</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>92.9047619047619</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10.95238095238095</v>
+      </c>
+      <c r="G45" t="n">
+        <v>103.8571428571428</v>
+      </c>
+      <c r="H45" t="n">
+        <v>82</v>
+      </c>
+      <c r="I45" t="n">
+        <v>21.85714285714285</v>
+      </c>
+      <c r="J45" t="n">
+        <v>131.1428571428571</v>
+      </c>
+      <c r="K45" t="n">
+        <v>131.1428571428571</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ORD45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>125.8888888888889</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6.111111111111111</v>
+      </c>
+      <c r="G46" t="n">
+        <v>132</v>
+      </c>
+      <c r="H46" t="n">
+        <v>110</v>
+      </c>
+      <c r="I46" t="n">
+        <v>22</v>
+      </c>
+      <c r="J46" t="n">
+        <v>220</v>
+      </c>
+      <c r="K46" t="n">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/Paintshop_Schedule_November.xlsx
+++ b/Paintshop_Schedule_November.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,7 +512,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -532,35 +532,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>17.09523809523809</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>9.523809523809524</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>26.61904761904762</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I3" t="n">
-        <v>4.61904761904762</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>55.42857142857144</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>55.42857142857144</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -584,13 +584,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>8.571428571428571</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>8.571428571428571</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>8.095238095238095</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>8.095238095238095</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="H5" t="n">
         <v>15</v>
@@ -653,31 +653,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>18.57142857142857</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>6.190476190476191</v>
+        <v>6.5</v>
       </c>
       <c r="G6" t="n">
-        <v>24.76190476190476</v>
+        <v>49.5</v>
       </c>
       <c r="H6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>121.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="7">
@@ -695,28 +695,28 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>24.11111111111111</v>
+        <v>30.55555555555556</v>
       </c>
       <c r="F7" t="n">
         <v>8.888888888888889</v>
       </c>
       <c r="G7" t="n">
-        <v>33</v>
+        <v>39.44444444444444</v>
       </c>
       <c r="H7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>8.444444444444443</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>92.88888888888887</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>92.88888888888887</v>
       </c>
     </row>
     <row r="8">
@@ -734,28 +734,28 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>24.76190476190476</v>
+        <v>31</v>
       </c>
       <c r="F8" t="n">
-        <v>6.666666666666667</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>31.42857142857143</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
         <v>35</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -766,35 +766,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>27.77777777777778</v>
+        <v>49.44444444444444</v>
       </c>
       <c r="F9" t="n">
         <v>11.66666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>39.44444444444444</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="H9" t="n">
         <v>38</v>
       </c>
       <c r="I9" t="n">
-        <v>1.444444444444443</v>
+        <v>23.11111111111111</v>
       </c>
       <c r="J9" t="n">
-        <v>18.77777777777776</v>
+        <v>300.4444444444444</v>
       </c>
       <c r="K9" t="n">
-        <v>18.77777777777776</v>
+        <v>300.4444444444444</v>
       </c>
     </row>
     <row r="10">
@@ -805,35 +805,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>17.22222222222222</v>
+        <v>37.66666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>10.55555555555556</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>27.77777777777778</v>
+        <v>45.58333333333333</v>
       </c>
       <c r="H10" t="n">
         <v>32</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>13.58333333333333</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>95.0833333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>95.0833333333333</v>
       </c>
     </row>
     <row r="11">
@@ -848,31 +848,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>27.61904761904762</v>
+        <v>49.58333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>5.714285714285714</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>33.33333333333334</v>
+        <v>54.58333333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>11.58333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>115.8333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>115.8333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -883,35 +883,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>8.333333333333334</v>
+        <v>17.08333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>12.77777777777778</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G12" t="n">
-        <v>21.11111111111111</v>
+        <v>26.66666666666666</v>
       </c>
       <c r="H12" t="n">
         <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>1.111111111111114</v>
+        <v>6.666666666666664</v>
       </c>
       <c r="J12" t="n">
-        <v>13.33333333333337</v>
+        <v>59.99999999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>13.33333333333337</v>
+        <v>59.99999999999998</v>
       </c>
     </row>
     <row r="13">
@@ -922,35 +922,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="F13" t="n">
         <v>12.22222222222222</v>
       </c>
       <c r="G13" t="n">
-        <v>12.22222222222222</v>
+        <v>26.55555555555556</v>
       </c>
       <c r="H13" t="n">
         <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>8.555555555555557</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>51.33333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>51.33333333333334</v>
       </c>
     </row>
     <row r="14">
@@ -961,35 +961,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>31.42857142857143</v>
+        <v>54.58333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>5.238095238095238</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>36.66666666666666</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>10.16666666666666</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>111.8333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>111.8333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -1007,28 +1007,28 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>38.66666666666666</v>
+        <v>49.5</v>
       </c>
       <c r="F15" t="n">
-        <v>11.90476190476191</v>
+        <v>12.5</v>
       </c>
       <c r="G15" t="n">
-        <v>50.57142857142857</v>
+        <v>62</v>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5714285714285694</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
-        <v>7.999999999999972</v>
+        <v>196</v>
       </c>
       <c r="K15" t="n">
-        <v>7.999999999999972</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16">
@@ -1039,35 +1039,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>52.33333333333334</v>
+        <v>62.11111111111111</v>
       </c>
       <c r="F16" t="n">
-        <v>11.42857142857143</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G16" t="n">
-        <v>63.76190476190477</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="H16" t="n">
         <v>66</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>9.444444444444443</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>84.99999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>84.99999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1078,35 +1078,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>52.66666666666666</v>
+        <v>70.91666666666666</v>
       </c>
       <c r="F17" t="n">
-        <v>8.888888888888889</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>61.55555555555556</v>
+        <v>77.58333333333333</v>
       </c>
       <c r="H17" t="n">
         <v>63</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>116.6666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>116.6666666666666</v>
       </c>
     </row>
     <row r="18">
@@ -1117,35 +1117,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>98</v>
+      </c>
+      <c r="F18" t="n">
         <v>7</v>
       </c>
-      <c r="E18" t="n">
-        <v>97.44444444444446</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7.777777777777778</v>
-      </c>
       <c r="G18" t="n">
-        <v>105.2222222222222</v>
+        <v>105</v>
       </c>
       <c r="H18" t="n">
         <v>85</v>
       </c>
       <c r="I18" t="n">
-        <v>20.22222222222223</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>262.888888888889</v>
+        <v>240</v>
       </c>
       <c r="K18" t="n">
-        <v>262.888888888889</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19">
@@ -1166,25 +1166,25 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>61.55555555555556</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="F19" t="n">
         <v>11.66666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>73.22222222222223</v>
+        <v>87.11111111111111</v>
       </c>
       <c r="H19" t="n">
         <v>78</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>9.111111111111114</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>91.11111111111114</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>91.11111111111114</v>
       </c>
     </row>
     <row r="20">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>58.11111111111111</v>
+        <v>77.58333333333333</v>
       </c>
       <c r="F20" t="n">
-        <v>11.11111111111111</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G20" t="n">
-        <v>69.22222222222221</v>
+        <v>85.91666666666666</v>
       </c>
       <c r="H20" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>11.91666666666666</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>178.7499999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>178.7499999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1238,31 +1238,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>50.57142857142857</v>
+        <v>79.5</v>
       </c>
       <c r="F21" t="n">
-        <v>7.142857142857143</v>
+        <v>7.5</v>
       </c>
       <c r="G21" t="n">
-        <v>57.71428571428572</v>
+        <v>87</v>
       </c>
       <c r="H21" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22">
@@ -1277,31 +1277,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>62.71428571428572</v>
+        <v>63</v>
       </c>
       <c r="F22" t="n">
-        <v>8.095238095238095</v>
+        <v>8.5</v>
       </c>
       <c r="G22" t="n">
-        <v>70.80952380952381</v>
+        <v>71.5</v>
       </c>
       <c r="H22" t="n">
         <v>69</v>
       </c>
       <c r="I22" t="n">
-        <v>1.80952380952381</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
-        <v>12.66666666666667</v>
+        <v>17.5</v>
       </c>
       <c r="K22" t="n">
-        <v>12.66666666666667</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="23">
@@ -1312,35 +1312,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>100.1111111111111</v>
+        <v>94.91666666666666</v>
       </c>
       <c r="F23" t="n">
-        <v>7.222222222222222</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>107.3333333333333</v>
+        <v>100.3333333333333</v>
       </c>
       <c r="H23" t="n">
         <v>86</v>
       </c>
       <c r="I23" t="n">
-        <v>21.33333333333334</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="J23" t="n">
-        <v>213.3333333333334</v>
+        <v>143.3333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>213.3333333333334</v>
+        <v>143.3333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -1351,35 +1351,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>97.47619047619047</v>
+        <v>103.3333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>8.571428571428571</v>
+        <v>7.5</v>
       </c>
       <c r="G24" t="n">
-        <v>106.047619047619</v>
+        <v>110.8333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I24" t="n">
-        <v>7.047619047619037</v>
+        <v>6.833333333333329</v>
       </c>
       <c r="J24" t="n">
-        <v>63.42857142857133</v>
+        <v>61.49999999999996</v>
       </c>
       <c r="K24" t="n">
-        <v>63.42857142857133</v>
+        <v>61.49999999999996</v>
       </c>
     </row>
     <row r="25">
@@ -1394,31 +1394,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>108.047619047619</v>
+        <v>106</v>
       </c>
       <c r="F25" t="n">
-        <v>9.047619047619047</v>
+        <v>9.5</v>
       </c>
       <c r="G25" t="n">
-        <v>117.0952380952381</v>
+        <v>115.5</v>
       </c>
       <c r="H25" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I25" t="n">
-        <v>11.09523809523809</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
-        <v>144.2380952380951</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>144.2380952380951</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -1429,35 +1429,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>38</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="F26" t="n">
-        <v>11.66666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G26" t="n">
-        <v>49.66666666666666</v>
+        <v>67.91666666666666</v>
       </c>
       <c r="H26" t="n">
         <v>53</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>14.91666666666666</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>208.8333333333332</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>208.8333333333332</v>
       </c>
     </row>
     <row r="27">
@@ -1468,35 +1468,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>78.22222222222223</v>
+        <v>87</v>
       </c>
       <c r="F27" t="n">
-        <v>12.22222222222222</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>90.44444444444446</v>
+        <v>98</v>
       </c>
       <c r="H27" t="n">
         <v>81</v>
       </c>
       <c r="I27" t="n">
-        <v>9.444444444444457</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>85.00000000000011</v>
+        <v>187</v>
       </c>
       <c r="K27" t="n">
-        <v>85.00000000000011</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
@@ -1511,31 +1511,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>65.76190476190476</v>
+        <v>85.91666666666666</v>
       </c>
       <c r="F28" t="n">
-        <v>5.714285714285714</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>71.47619047619047</v>
+        <v>90.91666666666666</v>
       </c>
       <c r="H28" t="n">
         <v>78</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>12.91666666666666</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>103.3333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>103.3333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -1546,698 +1546,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>86.52380952380952</v>
+        <v>92.11111111111111</v>
       </c>
       <c r="F29" t="n">
-        <v>10.95238095238095</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G29" t="n">
-        <v>97.47619047619047</v>
+        <v>104.8888888888889</v>
       </c>
       <c r="H29" t="n">
         <v>82</v>
       </c>
       <c r="I29" t="n">
-        <v>15.47619047619047</v>
+        <v>22.88888888888889</v>
       </c>
       <c r="J29" t="n">
-        <v>92.8571428571428</v>
+        <v>137.3333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>92.8571428571428</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ORD29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>11</v>
-      </c>
-      <c r="D30" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" t="n">
-        <v>119.4285714285714</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5.238095238095238</v>
-      </c>
-      <c r="G30" t="n">
-        <v>124.6666666666667</v>
-      </c>
-      <c r="H30" t="n">
-        <v>110</v>
-      </c>
-      <c r="I30" t="n">
-        <v>14.66666666666666</v>
-      </c>
-      <c r="J30" t="n">
-        <v>131.9999999999999</v>
-      </c>
-      <c r="K30" t="n">
-        <v>131.9999999999999</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ORD30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>12</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>124.6666666666667</v>
-      </c>
-      <c r="F31" t="n">
-        <v>11.42857142857143</v>
-      </c>
-      <c r="G31" t="n">
-        <v>136.0952380952381</v>
-      </c>
-      <c r="H31" t="n">
-        <v>115</v>
-      </c>
-      <c r="I31" t="n">
-        <v>21.09523809523807</v>
-      </c>
-      <c r="J31" t="n">
-        <v>274.238095238095</v>
-      </c>
-      <c r="K31" t="n">
-        <v>274.238095238095</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ORD31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>10</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>103.8571428571428</v>
-      </c>
-      <c r="F32" t="n">
-        <v>8.571428571428571</v>
-      </c>
-      <c r="G32" t="n">
-        <v>112.4285714285714</v>
-      </c>
-      <c r="H32" t="n">
-        <v>99</v>
-      </c>
-      <c r="I32" t="n">
-        <v>13.42857142857142</v>
-      </c>
-      <c r="J32" t="n">
-        <v>120.8571428571427</v>
-      </c>
-      <c r="K32" t="n">
-        <v>120.8571428571427</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ORD32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>9</v>
-      </c>
-      <c r="D33" t="n">
-        <v>5</v>
-      </c>
-      <c r="E33" t="n">
-        <v>112.3333333333333</v>
-      </c>
-      <c r="F33" t="n">
-        <v>10.55555555555556</v>
-      </c>
-      <c r="G33" t="n">
-        <v>122.8888888888889</v>
-      </c>
-      <c r="H33" t="n">
-        <v>106</v>
-      </c>
-      <c r="I33" t="n">
-        <v>16.8888888888889</v>
-      </c>
-      <c r="J33" t="n">
-        <v>202.6666666666668</v>
-      </c>
-      <c r="K33" t="n">
-        <v>202.6666666666668</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ORD33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" t="n">
-        <v>9</v>
-      </c>
-      <c r="E34" t="n">
-        <v>42.33333333333334</v>
-      </c>
-      <c r="F34" t="n">
-        <v>10</v>
-      </c>
-      <c r="G34" t="n">
-        <v>52.33333333333334</v>
-      </c>
-      <c r="H34" t="n">
-        <v>53</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ORD34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>7</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>71.47619047619047</v>
-      </c>
-      <c r="F35" t="n">
-        <v>10.47619047619048</v>
-      </c>
-      <c r="G35" t="n">
-        <v>81.95238095238095</v>
-      </c>
-      <c r="H35" t="n">
-        <v>80</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1.952380952380949</v>
-      </c>
-      <c r="J35" t="n">
-        <v>21.47619047619044</v>
-      </c>
-      <c r="K35" t="n">
-        <v>21.47619047619044</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ORD35</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>70.22222222222221</v>
-      </c>
-      <c r="F36" t="n">
-        <v>6.666666666666667</v>
-      </c>
-      <c r="G36" t="n">
-        <v>76.88888888888889</v>
-      </c>
-      <c r="H36" t="n">
-        <v>78</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ORD36</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>81.95238095238095</v>
-      </c>
-      <c r="F37" t="n">
-        <v>10.95238095238095</v>
-      </c>
-      <c r="G37" t="n">
-        <v>92.9047619047619</v>
-      </c>
-      <c r="H37" t="n">
-        <v>82</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10.9047619047619</v>
-      </c>
-      <c r="J37" t="n">
-        <v>65.42857142857139</v>
-      </c>
-      <c r="K37" t="n">
-        <v>65.42857142857139</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ORD37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>12</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>117.0952380952381</v>
-      </c>
-      <c r="F38" t="n">
-        <v>5.238095238095238</v>
-      </c>
-      <c r="G38" t="n">
-        <v>122.3333333333333</v>
-      </c>
-      <c r="H38" t="n">
-        <v>110</v>
-      </c>
-      <c r="I38" t="n">
-        <v>12.33333333333333</v>
-      </c>
-      <c r="J38" t="n">
-        <v>111</v>
-      </c>
-      <c r="K38" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ORD38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>11</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>126.7777777777778</v>
-      </c>
-      <c r="F39" t="n">
-        <v>13.33333333333333</v>
-      </c>
-      <c r="G39" t="n">
-        <v>140.1111111111111</v>
-      </c>
-      <c r="H39" t="n">
-        <v>115</v>
-      </c>
-      <c r="I39" t="n">
-        <v>25.11111111111111</v>
-      </c>
-      <c r="J39" t="n">
-        <v>326.4444444444445</v>
-      </c>
-      <c r="K39" t="n">
-        <v>326.4444444444445</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ORD39</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>9</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>105.2222222222222</v>
-      </c>
-      <c r="F40" t="n">
-        <v>10</v>
-      </c>
-      <c r="G40" t="n">
-        <v>115.2222222222222</v>
-      </c>
-      <c r="H40" t="n">
-        <v>99</v>
-      </c>
-      <c r="I40" t="n">
-        <v>16.22222222222223</v>
-      </c>
-      <c r="J40" t="n">
-        <v>146.0000000000001</v>
-      </c>
-      <c r="K40" t="n">
-        <v>146.0000000000001</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ORD40</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>10</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>116.2222222222222</v>
-      </c>
-      <c r="F41" t="n">
-        <v>10.55555555555556</v>
-      </c>
-      <c r="G41" t="n">
-        <v>126.7777777777778</v>
-      </c>
-      <c r="H41" t="n">
-        <v>106</v>
-      </c>
-      <c r="I41" t="n">
-        <v>20.77777777777779</v>
-      </c>
-      <c r="J41" t="n">
-        <v>249.3333333333334</v>
-      </c>
-      <c r="K41" t="n">
-        <v>249.3333333333334</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ORD41</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>4</v>
-      </c>
-      <c r="D42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E42" t="n">
-        <v>46.44444444444444</v>
-      </c>
-      <c r="F42" t="n">
-        <v>11.66666666666667</v>
-      </c>
-      <c r="G42" t="n">
-        <v>58.11111111111111</v>
-      </c>
-      <c r="H42" t="n">
-        <v>53</v>
-      </c>
-      <c r="I42" t="n">
-        <v>5.111111111111107</v>
-      </c>
-      <c r="J42" t="n">
-        <v>71.5555555555555</v>
-      </c>
-      <c r="K42" t="n">
-        <v>71.5555555555555</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ORD42</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>7</v>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="n">
-        <v>86.88888888888889</v>
-      </c>
-      <c r="F43" t="n">
-        <v>12.22222222222222</v>
-      </c>
-      <c r="G43" t="n">
-        <v>99.11111111111111</v>
-      </c>
-      <c r="H43" t="n">
-        <v>81</v>
-      </c>
-      <c r="I43" t="n">
-        <v>18.11111111111111</v>
-      </c>
-      <c r="J43" t="n">
-        <v>199.2222222222223</v>
-      </c>
-      <c r="K43" t="n">
-        <v>199.2222222222223</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ORD43</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>8</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>71.80952380952381</v>
-      </c>
-      <c r="F44" t="n">
-        <v>5.714285714285714</v>
-      </c>
-      <c r="G44" t="n">
-        <v>77.52380952380952</v>
-      </c>
-      <c r="H44" t="n">
-        <v>78</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ORD44</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>9</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>92.9047619047619</v>
-      </c>
-      <c r="F45" t="n">
-        <v>10.95238095238095</v>
-      </c>
-      <c r="G45" t="n">
-        <v>103.8571428571428</v>
-      </c>
-      <c r="H45" t="n">
-        <v>82</v>
-      </c>
-      <c r="I45" t="n">
-        <v>21.85714285714285</v>
-      </c>
-      <c r="J45" t="n">
-        <v>131.1428571428571</v>
-      </c>
-      <c r="K45" t="n">
-        <v>131.1428571428571</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ORD45</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>10</v>
-      </c>
-      <c r="D46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" t="n">
-        <v>125.8888888888889</v>
-      </c>
-      <c r="F46" t="n">
-        <v>6.111111111111111</v>
-      </c>
-      <c r="G46" t="n">
-        <v>132</v>
-      </c>
-      <c r="H46" t="n">
-        <v>110</v>
-      </c>
-      <c r="I46" t="n">
-        <v>22</v>
-      </c>
-      <c r="J46" t="n">
-        <v>220</v>
-      </c>
-      <c r="K46" t="n">
-        <v>220</v>
+        <v>137.3333333333333</v>
       </c>
     </row>
   </sheetData>
